--- a/MappingViewer.Web/Data/Sample.xlsx
+++ b/MappingViewer.Web/Data/Sample.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20400" windowHeight="6900" activeTab="4"/>
+    <workbookView windowWidth="20400" windowHeight="6900" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="Employees" sheetId="1" r:id="rId1"/>
@@ -12,6 +12,7 @@
     <sheet name="Orders" sheetId="3" r:id="rId3"/>
     <sheet name="Customers" sheetId="4" r:id="rId4"/>
     <sheet name="Suppliers" sheetId="5" r:id="rId5"/>
+    <sheet name="Sheet1" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -31,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="315" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="384" uniqueCount="51">
   <si>
     <t>Employee roster</t>
   </si>
@@ -139,6 +140,51 @@
   </si>
   <si>
     <t>iiijijdd</t>
+  </si>
+  <si>
+    <t>asdasd</t>
+  </si>
+  <si>
+    <t>s</t>
+  </si>
+  <si>
+    <t>d</t>
+  </si>
+  <si>
+    <t>f</t>
+  </si>
+  <si>
+    <t>g</t>
+  </si>
+  <si>
+    <t>y</t>
+  </si>
+  <si>
+    <t>ad</t>
+  </si>
+  <si>
+    <t>saad</t>
+  </si>
+  <si>
+    <t>TH1</t>
+  </si>
+  <si>
+    <t>TH2</t>
+  </si>
+  <si>
+    <t>Data Type (Object)</t>
+  </si>
+  <si>
+    <t>assdfsdfsd</t>
+  </si>
+  <si>
+    <t>sdfsdfd</t>
+  </si>
+  <si>
+    <t>SCM Field</t>
+  </si>
+  <si>
+    <t>b</t>
   </si>
 </sst>
 </file>
@@ -151,10 +197,16 @@
     <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="179" formatCode="_ &quot;₹&quot;* #,##0_ ;_ &quot;₹&quot;* \-#,##0_ ;_ &quot;₹&quot;* &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FFA31515"/>
+      <name val="Consolas"/>
       <charset val="134"/>
     </font>
     <font>
@@ -630,154 +682,155 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFill="0" applyBorder="0"/>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
@@ -1323,7 +1376,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
@@ -1372,24 +1425,24 @@
       </c>
     </row>
     <row r="10" spans="1:5">
-      <c r="A10" s="2" t="s">
+      <c r="A10" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B10" s="2"/>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
+      <c r="B10" s="3"/>
+      <c r="C10" s="3"/>
+      <c r="D10" s="3"/>
     </row>
     <row r="11" spans="1:5">
-      <c r="A11" s="3" t="s">
+      <c r="A11" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="C11" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D11" s="3" t="s">
+      <c r="D11" s="4" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1474,24 +1527,24 @@
       </c>
     </row>
     <row r="19" spans="1:4">
-      <c r="A19" s="2" t="s">
+      <c r="A19" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B19" s="2"/>
-      <c r="C19" s="2"/>
-      <c r="D19" s="2"/>
+      <c r="B19" s="3"/>
+      <c r="C19" s="3"/>
+      <c r="D19" s="3"/>
     </row>
     <row r="20" spans="1:4">
-      <c r="A20" s="3" t="s">
+      <c r="A20" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="B20" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="C20" s="3" t="s">
+      <c r="C20" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D20" s="3" t="s">
+      <c r="D20" s="4" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1584,7 +1637,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
@@ -1608,8 +1661,6 @@
       <c r="A4" t="s">
         <v>5</v>
       </c>
-      <c r="B4"/>
-      <c r="C4"/>
       <c r="D4" t="s">
         <v>3</v>
       </c>
@@ -1635,24 +1686,24 @@
       </c>
     </row>
     <row r="10" spans="1:5">
-      <c r="A10" s="2" t="s">
+      <c r="A10" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B10" s="2"/>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
+      <c r="B10" s="3"/>
+      <c r="C10" s="3"/>
+      <c r="D10" s="3"/>
     </row>
     <row r="11" spans="1:5">
-      <c r="A11" s="3" t="s">
+      <c r="A11" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="C11" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D11" s="3" t="s">
+      <c r="D11" s="4" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1737,24 +1788,24 @@
       </c>
     </row>
     <row r="19" spans="1:4">
-      <c r="A19" s="2" t="s">
+      <c r="A19" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B19" s="2"/>
-      <c r="C19" s="2"/>
-      <c r="D19" s="2"/>
+      <c r="B19" s="3"/>
+      <c r="C19" s="3"/>
+      <c r="D19" s="3"/>
     </row>
     <row r="20" spans="1:4">
-      <c r="A20" s="3" t="s">
+      <c r="A20" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="B20" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="C20" s="3" t="s">
+      <c r="C20" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D20" s="3" t="s">
+      <c r="D20" s="4" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1846,7 +1897,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
@@ -1870,8 +1921,6 @@
       <c r="A4" t="s">
         <v>5</v>
       </c>
-      <c r="B4"/>
-      <c r="C4"/>
       <c r="D4" t="s">
         <v>3</v>
       </c>
@@ -1897,24 +1946,24 @@
       </c>
     </row>
     <row r="10" spans="1:5">
-      <c r="A10" s="2" t="s">
+      <c r="A10" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B10" s="2"/>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
+      <c r="B10" s="3"/>
+      <c r="C10" s="3"/>
+      <c r="D10" s="3"/>
     </row>
     <row r="11" spans="1:5">
-      <c r="A11" s="3" t="s">
+      <c r="A11" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="C11" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D11" s="3" t="s">
+      <c r="D11" s="4" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1999,24 +2048,24 @@
       </c>
     </row>
     <row r="19" spans="1:4">
-      <c r="A19" s="2" t="s">
+      <c r="A19" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B19" s="2"/>
-      <c r="C19" s="2"/>
-      <c r="D19" s="2"/>
+      <c r="B19" s="3"/>
+      <c r="C19" s="3"/>
+      <c r="D19" s="3"/>
     </row>
     <row r="20" spans="1:4">
-      <c r="A20" s="3" t="s">
+      <c r="A20" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="B20" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="C20" s="3" t="s">
+      <c r="C20" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D20" s="3" t="s">
+      <c r="D20" s="4" t="s">
         <v>14</v>
       </c>
     </row>
@@ -2109,7 +2158,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
@@ -2133,8 +2182,6 @@
       <c r="A4" t="s">
         <v>5</v>
       </c>
-      <c r="B4"/>
-      <c r="C4"/>
       <c r="D4" t="s">
         <v>3</v>
       </c>
@@ -2160,24 +2207,24 @@
       </c>
     </row>
     <row r="10" spans="1:5">
-      <c r="A10" s="2" t="s">
+      <c r="A10" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B10" s="2"/>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
+      <c r="B10" s="3"/>
+      <c r="C10" s="3"/>
+      <c r="D10" s="3"/>
     </row>
     <row r="11" spans="1:5">
-      <c r="A11" s="3" t="s">
+      <c r="A11" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="C11" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D11" s="3" t="s">
+      <c r="D11" s="4" t="s">
         <v>14</v>
       </c>
     </row>
@@ -2262,24 +2309,24 @@
       </c>
     </row>
     <row r="19" spans="1:4">
-      <c r="A19" s="2" t="s">
+      <c r="A19" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B19" s="2"/>
-      <c r="C19" s="2"/>
-      <c r="D19" s="2"/>
+      <c r="B19" s="3"/>
+      <c r="C19" s="3"/>
+      <c r="D19" s="3"/>
     </row>
     <row r="20" spans="1:4">
-      <c r="A20" s="3" t="s">
+      <c r="A20" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="B20" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="C20" s="3" t="s">
+      <c r="C20" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D20" s="3" t="s">
+      <c r="D20" s="4" t="s">
         <v>14</v>
       </c>
     </row>
@@ -2362,8 +2409,8 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E25"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="4"/>
+  <dimension ref="A1:J38"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.0571428571429" customWidth="1"/>
     <col min="2" max="2" width="17.2761904761905" customWidth="1"/>
@@ -2371,15 +2418,15 @@
     <col min="4" max="4" width="9.14285714285714" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:10">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:10">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -2387,106 +2434,122 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:10">
       <c r="A3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:10">
       <c r="A4" t="s">
         <v>5</v>
       </c>
-      <c r="B4"/>
-      <c r="C4"/>
       <c r="D4" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:10">
       <c r="A5" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:10">
       <c r="A6" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:10">
       <c r="A7" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="1:5">
+    <row r="9" spans="1:10">
       <c r="A9" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:5">
-      <c r="A10" s="2" t="s">
+    <row r="10" spans="1:10">
+      <c r="A10" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B10" s="2"/>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
-    </row>
-    <row r="11" spans="1:5">
-      <c r="A11" s="3" t="s">
+      <c r="B10" s="3"/>
+      <c r="C10" s="3"/>
+      <c r="D10" s="3"/>
+    </row>
+    <row r="11" spans="1:10">
+      <c r="A11" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="C11" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D11" s="3" t="s">
+      <c r="D11" s="4" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="12" spans="1:5">
+      <c r="E11" t="s">
+        <v>36</v>
+      </c>
+      <c r="F11" t="s">
+        <v>37</v>
+      </c>
+      <c r="G11" t="s">
+        <v>38</v>
+      </c>
+      <c r="H11" t="s">
+        <v>39</v>
+      </c>
+      <c r="I11" t="s">
+        <v>40</v>
+      </c>
+      <c r="J11" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10">
       <c r="A12" t="s">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="B12" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="C12" t="s">
         <v>17</v>
       </c>
       <c r="D12" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10">
       <c r="A13" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="B13" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="C13" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D13" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10">
       <c r="A14" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="B14" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="C14" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="D14" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10">
       <c r="A15" t="s">
         <v>27</v>
       </c>
@@ -2500,7 +2563,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="16" spans="1:5">
+    <row r="16" spans="1:10">
       <c r="A16" t="s">
         <v>30</v>
       </c>
@@ -2516,76 +2579,100 @@
     </row>
     <row r="17" spans="1:4">
       <c r="A17" t="s">
-        <v>34</v>
+        <v>27</v>
+      </c>
+      <c r="B17" t="s">
+        <v>28</v>
+      </c>
+      <c r="C17" t="s">
+        <v>17</v>
+      </c>
+      <c r="D17" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="18" spans="1:4">
       <c r="A18" t="s">
-        <v>35</v>
+        <v>27</v>
+      </c>
+      <c r="B18" t="s">
+        <v>28</v>
+      </c>
+      <c r="C18" t="s">
+        <v>17</v>
+      </c>
+      <c r="D18" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="19" spans="1:4">
-      <c r="A19" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B19" s="2"/>
-      <c r="C19" s="2"/>
-      <c r="D19" s="2"/>
+      <c r="A19" t="s">
+        <v>27</v>
+      </c>
+      <c r="B19" t="s">
+        <v>28</v>
+      </c>
+      <c r="C19" t="s">
+        <v>17</v>
+      </c>
+      <c r="D19" t="s">
+        <v>29</v>
+      </c>
     </row>
     <row r="20" spans="1:4">
-      <c r="A20" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>14</v>
+      <c r="A20" t="s">
+        <v>27</v>
+      </c>
+      <c r="B20" t="s">
+        <v>28</v>
+      </c>
+      <c r="C20" t="s">
+        <v>17</v>
+      </c>
+      <c r="D20" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="21" spans="1:4">
       <c r="A21" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="B21" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="C21" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="D21" t="s">
-        <v>18</v>
+        <v>33</v>
       </c>
     </row>
     <row r="22" spans="1:4">
       <c r="A22" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="B22" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="C22" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D22" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
     </row>
     <row r="23" spans="1:4">
       <c r="A23" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="B23" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="C23" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="D23" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2604,16 +2691,287 @@
     </row>
     <row r="25" spans="1:4">
       <c r="A25" t="s">
+        <v>27</v>
+      </c>
+      <c r="B25" t="s">
+        <v>28</v>
+      </c>
+      <c r="C25" t="s">
+        <v>17</v>
+      </c>
+      <c r="D25" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4">
+      <c r="A26" t="s">
         <v>30</v>
       </c>
-      <c r="B25" t="s">
+      <c r="B26" t="s">
         <v>31</v>
       </c>
-      <c r="C25" t="s">
+      <c r="C26" t="s">
         <v>32</v>
       </c>
-      <c r="D25" t="s">
+      <c r="D26" t="s">
         <v>33</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4">
+      <c r="A30" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4">
+      <c r="A31" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4">
+      <c r="A32" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B32" s="3"/>
+      <c r="C32" s="3"/>
+      <c r="D32" s="3"/>
+    </row>
+    <row r="33" spans="1:4">
+      <c r="A33" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D33" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4">
+      <c r="A34" t="s">
+        <v>15</v>
+      </c>
+      <c r="B34" t="s">
+        <v>16</v>
+      </c>
+      <c r="C34" t="s">
+        <v>17</v>
+      </c>
+      <c r="D34" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4">
+      <c r="A35" t="s">
+        <v>19</v>
+      </c>
+      <c r="B35" t="s">
+        <v>20</v>
+      </c>
+      <c r="C35" t="s">
+        <v>21</v>
+      </c>
+      <c r="D35" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4">
+      <c r="A36" t="s">
+        <v>23</v>
+      </c>
+      <c r="B36" t="s">
+        <v>24</v>
+      </c>
+      <c r="C36" t="s">
+        <v>25</v>
+      </c>
+      <c r="D36" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4">
+      <c r="A37" t="s">
+        <v>27</v>
+      </c>
+      <c r="B37" t="s">
+        <v>28</v>
+      </c>
+      <c r="C37" t="s">
+        <v>17</v>
+      </c>
+      <c r="D37" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4">
+      <c r="A38" t="s">
+        <v>30</v>
+      </c>
+      <c r="B38" t="s">
+        <v>31</v>
+      </c>
+      <c r="C38" t="s">
+        <v>32</v>
+      </c>
+      <c r="D38" t="s">
+        <v>33</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:F13"/>
+  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelCol="5"/>
+  <cols>
+    <col min="1" max="1" width="5.57142857142857" customWidth="1"/>
+    <col min="2" max="2" width="4.85714285714286" customWidth="1"/>
+    <col min="3" max="3" width="20.7142857142857" customWidth="1"/>
+    <col min="4" max="4" width="11" customWidth="1"/>
+    <col min="5" max="5" width="8.14285714285714" customWidth="1"/>
+    <col min="6" max="6" width="10.5714285714286" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6">
+      <c r="A1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" t="s">
+        <v>44</v>
+      </c>
+      <c r="B8" t="s">
+        <v>45</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D8" t="s">
+        <v>47</v>
+      </c>
+      <c r="E8" t="s">
+        <v>48</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9">
+        <v>1</v>
+      </c>
+      <c r="B9">
+        <v>2</v>
+      </c>
+      <c r="C9">
+        <v>3</v>
+      </c>
+      <c r="D9">
+        <v>6</v>
+      </c>
+      <c r="E9" t="s">
+        <v>50</v>
+      </c>
+      <c r="F9" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10">
+        <v>2</v>
+      </c>
+      <c r="B10">
+        <v>3</v>
+      </c>
+      <c r="C10">
+        <v>4</v>
+      </c>
+      <c r="D10" t="s">
+        <v>40</v>
+      </c>
+      <c r="E10" t="s">
+        <v>40</v>
+      </c>
+      <c r="F10" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11">
+        <v>3</v>
+      </c>
+      <c r="B11">
+        <v>4</v>
+      </c>
+      <c r="C11">
+        <v>5</v>
+      </c>
+      <c r="D11" t="s">
+        <v>40</v>
+      </c>
+      <c r="E11" t="s">
+        <v>40</v>
+      </c>
+      <c r="F11" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12">
+        <v>4</v>
+      </c>
+      <c r="B12">
+        <v>5</v>
+      </c>
+      <c r="C12">
+        <v>6</v>
+      </c>
+      <c r="D12" t="s">
+        <v>40</v>
+      </c>
+      <c r="E12" t="s">
+        <v>40</v>
+      </c>
+      <c r="F12" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13">
+        <v>5</v>
+      </c>
+      <c r="B13">
+        <v>6</v>
+      </c>
+      <c r="C13">
+        <v>7</v>
+      </c>
+      <c r="D13" t="s">
+        <v>40</v>
+      </c>
+      <c r="E13" t="s">
+        <v>40</v>
+      </c>
+      <c r="F13" t="s">
+        <v>40</v>
       </c>
     </row>
   </sheetData>
